--- a/sampleForm/排班表基礎表格.xlsx
+++ b/sampleForm/排班表基礎表格.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hsontech-my.sharepoint.com/personal/hson_evan_kutech_tw/Documents/桌面/排班表/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Evan\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{DAE3EE9E-D2F5-4970-AAB5-E93D51486E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AFCA272-21DD-4B00-B3E8-3E2BA91E3FD1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FC3D73-CDA0-4047-A937-DE58F34C46B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FDC2DBF7-FF9B-4DB6-9DF2-878F9641F8B1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDC2DBF7-FF9B-4DB6-9DF2-878F9641F8B1}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -81,14 +81,14 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="標楷體"/>
       <family val="4"/>
       <charset val="136"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="標楷體"/>
       <family val="4"/>
@@ -219,35 +219,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -563,422 +563,422 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC29B112-7418-4827-B870-679948A302E8}">
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr defaultRowHeight="27.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="23.375" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3"/>
+    <col min="1" max="7" width="23.375" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>2</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>3</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>4</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>5</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>6</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>9</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>10</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>11</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="5">
         <v>12</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="5">
         <v>13</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="5">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="5">
         <v>15</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <v>16</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>17</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>18</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="5">
         <v>19</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="5">
         <v>20</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="5">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
+      <c r="A24" s="5">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5">
+        <v>23</v>
+      </c>
+      <c r="C24" s="5">
+        <v>24</v>
+      </c>
+      <c r="D24" s="5">
+        <v>25</v>
+      </c>
+      <c r="E24" s="5">
+        <v>26</v>
+      </c>
+      <c r="F24" s="5">
+        <v>27</v>
+      </c>
+      <c r="G24" s="5">
+        <v>28</v>
+      </c>
     </row>
     <row r="25" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>22</v>
-      </c>
-      <c r="B25" s="7">
-        <v>23</v>
-      </c>
-      <c r="C25" s="7">
-        <v>24</v>
-      </c>
-      <c r="D25" s="7">
-        <v>25</v>
-      </c>
-      <c r="E25" s="7">
-        <v>26</v>
-      </c>
-      <c r="F25" s="7">
-        <v>27</v>
-      </c>
-      <c r="G25" s="7">
-        <v>28</v>
-      </c>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
+      <c r="A31" s="5">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5">
+        <v>30</v>
+      </c>
+      <c r="C31" s="5">
+        <v>31</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5">
+        <v>2</v>
+      </c>
+      <c r="F31" s="5">
+        <v>3</v>
+      </c>
+      <c r="G31" s="5">
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
     </row>
     <row r="33" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
-        <v>29</v>
-      </c>
-      <c r="B33" s="7">
-        <v>30</v>
-      </c>
-      <c r="C33" s="7">
-        <v>31</v>
-      </c>
-      <c r="D33" s="7">
-        <v>1</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2</v>
-      </c>
-      <c r="F33" s="7">
-        <v>3</v>
-      </c>
-      <c r="G33" s="7">
-        <v>4</v>
-      </c>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
     </row>
     <row r="36" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
     </row>
     <row r="37" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
@@ -989,38 +989,12 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-    </row>
-    <row r="39" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-    </row>
-    <row r="40" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>